--- a/human_resources_forms/003_leadership_practice_inventory_questionnaire--human_resources_forms.xlsx
+++ b/human_resources_forms/003_leadership_practice_inventory_questionnaire--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,20 +525,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>What is your leadership style (e.g. democratic, autocratic, laissez-faire)?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>Which of the following areas do you struggle with the most?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,43 +571,43 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>How would you rate your ability to adapt to change?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_4</t>
+          <t>leadership_practice_inventoryquestionnaire_page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>How would you rate your emotional intelligence (e.g. empathy, self-awareness)?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>What is the most significant leadership challenge you face?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,30 +630,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_6</t>
+          <t>leadership_practice_inventoryquestionnaire_page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>How do you typically handle conflict or difficult situations?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>How often do you involve others in your decision-making process?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_8</t>
+          <t>leadership_practice_inventoryquestionnaire_page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>How would you rate your ability to set and achieve goals?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,23 +699,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_9</t>
+          <t>leadership_practice_inventoryquestionnaire_page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>What are some common barriers to your leadership practice?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_10</t>
+          <t>leadership_practice_inventoryquestionnaire_page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>Who is your primary role model or mentor?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,41 +750,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_11</t>
+          <t>leadership_practice_inventoryquestionnaire_page_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>How can you be of most value to your team?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_12</t>
+          <t>leadership_practice_inventoryquestionnaire_page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>Which leadership development opportunities would you like to pursue in the next 6 months?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,81 +796,81 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_13</t>
+          <t>leadership_practice_inventoryquestionnaire_page_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>How do you rate your ability to delegate tasks?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_14</t>
+          <t>leadership_practice_inventoryquestionnaire_page_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>What are some common challenges faced by your team?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_15</t>
+          <t>leadership_practice_inventoryquestionnaire_page_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>How often do you communicate with your team?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_16</t>
+          <t>leadership_practice_inventoryquestionnaire_page_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>How do you handle conflicts between team members?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_17</t>
+          <t>leadership_practice_inventoryquestionnaire_page_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>leadership_practice_inventoryquestionnaire</t>
+          <t>How do you ensure that your team members are developing their skills?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,179 +911,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_18</t>
+          <t>leadership_practice_inventoryquestionnaire_page_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire</t>
+          <t>How can you improve your own leadership style in the next 6 months?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>leadership_practice_inventory_questionnaire_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>leadership_practice_inventoryquestionnaire</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>leadership_practice_inventory_questionnaire_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>leadership_practice_inventoryquestionnaire</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>leadership_practice_inventory_questionnaire_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>leadership_practice_inventory_questionnaire</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>leadership_practice_inventoryquestionnaire</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>leadership_practice_inventory_questionnaire</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>leadership_practice_inventory_questionnaire_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>leadership_practice_inventoryquestionnaire</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>leadership_practice_inventory_questionnaire_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>leadership_practice_inventoryquestionnaire</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>leadership_practice_inventory_questionnaire_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>leadership_practice_inventoryquestionnaire</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,357 +965,510 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_4_choices</t>
+          <t>leadership_practice_inventory_questionnaire_page_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>autocratic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Autocratic</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_4_choices</t>
+          <t>leadership_practice_inventory_questionnaire_page_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>democratic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Democratic</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_4_choices</t>
+          <t>leadership_practice_inventory_questionnaire_page_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>laissez-faire</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Laissez-faire</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_9_choices</t>
+          <t>leadership_practice_inventory_questionnaire_page_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_9_choices</t>
+          <t>leadership_practice_inventory_questionnaire_page_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>decision-making</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Decision-making</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_9_choices</t>
+          <t>leadership_practice_inventory_questionnaire_page_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>team_management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Team management</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_11_choices</t>
+          <t>leadership_practice_inventoryquestionnaire_page_6_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>collaborative_approach</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Collaborative approach</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_11_choices</t>
+          <t>leadership_practice_inventoryquestionnaire_page_6_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>competitive_approach</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Competitive approach</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_11_choices</t>
+          <t>leadership_practice_inventoryquestionnaire_page_6_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>avoidance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Avoidance</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_14_choices</t>
+          <t>leadership_practice_inventory_questionnaire_page_7_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_14_choices</t>
+          <t>leadership_practice_inventory_questionnaire_page_7_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_14_choices</t>
+          <t>leadership_practice_inventory_questionnaire_page_7_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_16_choices</t>
+          <t>leadership_practice_inventoryquestionnaire_page_11_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>providing_feedback_and_guidance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Providing feedback and guidance</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_16_choices</t>
+          <t>leadership_practice_inventoryquestionnaire_page_11_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>coaching_and_developing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Coaching and developing</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_16_choices</t>
+          <t>leadership_practice_inventoryquestionnaire_page_11_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>supporting_and_motivating</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Supporting and motivating</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_21_choices</t>
+          <t>leadership_practice_inventoryquestionnaire_page_11_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>leading_by_example</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Leading by example</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_21_choices</t>
+          <t>leadership_practice_inventoryquestionnaire_page_12_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>coaching_or_mentoring</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Coaching or mentoring</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_21_choices</t>
+          <t>leadership_practice_inventoryquestionnaire_page_12_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>leadership_development_programs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Leadership development programs</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_24_choices</t>
+          <t>leadership_practice_inventoryquestionnaire_page_12_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>training_or_workshops</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Training or workshops</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_24_choices</t>
+          <t>leadership_practice_inventoryquestionnaire_page_12_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>education_or_courses</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Education or courses</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>leadership_practice_inventory_questionnaire_page_24_choices</t>
+          <t>leadership_practice_inventoryquestionnaire_page_15_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Frequently</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>leadership_practice_inventoryquestionnaire_page_15_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>leadership_practice_inventoryquestionnaire_page_15_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>leadership_practice_inventoryquestionnaire_page_16_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>collaborative_approach</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Collaborative approach</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>leadership_practice_inventoryquestionnaire_page_16_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>competitive_approach</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Competitive approach</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>leadership_practice_inventoryquestionnaire_page_16_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avoidance</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Avoidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>leadership_practice_inventoryquestionnaire_page_17_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>coaching</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Coaching</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>leadership_practice_inventoryquestionnaire_page_17_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>mentoring</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>leadership_practice_inventoryquestionnaire_page_17_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>providing_feedback</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Providing feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>leadership_practice_inventoryquestionnaire_page_17_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Training</t>
         </is>
       </c>
     </row>
